--- a/astro-site/public/dl/restaurant-business-plan/restaurant-opening-checklist.xlsx
+++ b/astro-site/public/dl/restaurant-business-plan/restaurant-opening-checklist.xlsx
@@ -963,7 +963,7 @@
       <c r="E14" s="12" t="inlineStr"/>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Registration steps and unemployment insurance rates vary by state: confirm them with your state workforce agency and your accountant before your first payroll</t>
+          <t>Owners of an LLC or sole proprietorship are not on payroll: they take draws and pay self-employment tax. Ask your accountant how to set it up</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="59.75" customHeight="1">
+    <row r="17" ht="104.75" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Premises</t>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Sign the commercial lease</t>
+          <t>Sign the commercial lease and file the liquor license application right after (state alcohol agency + local approval)</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1031,7 +1031,7 @@
       <c r="E17" s="12" t="inlineStr"/>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Review the clauses: term, rent, NNN / CAM charges, personal guarantee and build-out allowance. Have an attorney read it</t>
+          <t>Review term, rent, NNN / CAM charges, personal guarantee and build-out allowance with an attorney. Liquor license applications usually ask for proof that you control the premises: file yours as soon as the lease is signed</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       <c r="E21" s="12" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Most health departments want a plan review of your layout and equipment BEFORE you build out; a restaurant gets a food establishment permit and an inspection before opening. UK: register your food business with the council at least 28 days before you start (free) and expect a Food Hygiene Rating (1-5) after inspection in England, Wales and Northern Ireland; Scotland uses FHIS (Pass / Improvement Required)</t>
+          <t>Most health departments want a plan review of your layout and equipment BEFORE you build out; a restaurant gets a food establishment permit and an inspection before opening. UK: register your food business with the council at least 28 days before you start (free) and expect a Food Hygiene Rating (0-5) after inspection in England, Wales and Northern Ireland; Scotland uses FHIS (Pass / Improvement Required)</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -2123,7 +2123,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="134.75" customHeight="1">
+    <row r="60" ht="149.5" customHeight="1">
       <c r="A60" s="17" t="inlineStr">
         <is>
           <t>Legal</t>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Liquor license (state alcohol agency + local approval) and age-restriction signage</t>
+          <t>Liquor license issued and posted before opening, with age-restriction signage</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
@@ -2141,13 +2141,13 @@
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>1 day</t>
+          <t>Start in Phase 2: often 3-12 months</t>
         </is>
       </c>
       <c r="E60" s="16" t="n"/>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>Rules differ by state: apply early. In quota states you buy an existing license instead of applying for a new one. Many states and insurers expect responsible beverage service training (for example TIPS or ServSafe Alcohol), and the age notice goes where your state says</t>
+          <t>Applied for in Phase 2, right after the lease is signed. In quota states you buy an existing license instead. Many states and insurers expect responsible beverage service training (for example TIPS or ServSafe Alcohol); post the age notice where your state says, and serve no alcohol until the license is issued</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
